--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121112051</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>121111905</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112051</v>
+        <v>121111917</v>
       </c>
       <c r="B2" t="n">
         <v>79219</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572975</v>
+        <v>572965</v>
       </c>
       <c r="R2" t="n">
-        <v>6512353</v>
+        <v>6512318</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111993</v>
+        <v>121112051</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,33 +789,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -828,7 +823,7 @@
         <v>6512353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111905</v>
+        <v>121111993</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572965</v>
+        <v>572975</v>
       </c>
       <c r="R4" t="n">
-        <v>6512318</v>
+        <v>6512353</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121111917</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112051</v>
+        <v>121112030</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111917</v>
+        <v>121112030</v>
       </c>
       <c r="B2" t="n">
         <v>79222</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572965</v>
+        <v>572975</v>
       </c>
       <c r="R2" t="n">
-        <v>6512318</v>
+        <v>6512353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112030</v>
+        <v>121111993</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,28 +789,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -823,7 +828,7 @@
         <v>6512353</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111993</v>
+        <v>121111905</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>79222</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572975</v>
+        <v>572965</v>
       </c>
       <c r="R4" t="n">
-        <v>6512353</v>
+        <v>6512318</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112030</v>
+        <v>121111993</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>8435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -721,7 +726,7 @@
         <v>6512353</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111993</v>
+        <v>121112030</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>79225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,33 +794,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -828,7 +828,7 @@
         <v>6512353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111905</v>
+        <v>121111917</v>
       </c>
       <c r="B4" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111993</v>
+        <v>121112030</v>
       </c>
       <c r="B2" t="n">
-        <v>8435</v>
+        <v>79225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -726,7 +721,7 @@
         <v>6512353</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112030</v>
+        <v>121111905</v>
       </c>
       <c r="B3" t="n">
         <v>79225</v>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572975</v>
+        <v>572965</v>
       </c>
       <c r="R3" t="n">
-        <v>6512353</v>
+        <v>6512318</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111917</v>
+        <v>121111993</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>8435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572965</v>
+        <v>572975</v>
       </c>
       <c r="R4" t="n">
-        <v>6512318</v>
+        <v>6512353</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>

--- a/artfynd/A 43306-2024 artfynd.xlsx
+++ b/artfynd/A 43306-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112030</v>
+        <v>121111905</v>
       </c>
       <c r="B2" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572975</v>
+        <v>572965</v>
       </c>
       <c r="R2" t="n">
-        <v>6512353</v>
+        <v>6512318</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111905</v>
+        <v>121112030</v>
       </c>
       <c r="B3" t="n">
-        <v>79225</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572965</v>
+        <v>572975</v>
       </c>
       <c r="R3" t="n">
-        <v>6512318</v>
+        <v>6512353</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,12 +872,7 @@
         <v>121111993</v>
       </c>
       <c r="B4" t="n">
-        <v>8435</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
